--- a/output/yearly_population_iteration_50_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_50_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6468</v>
+        <v>6017</v>
       </c>
       <c r="C2" t="n">
-        <v>5375</v>
+        <v>7522</v>
       </c>
       <c r="D2" t="n">
-        <v>32395</v>
+        <v>31125</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3749</v>
+        <v>4180</v>
       </c>
       <c r="C3" t="n">
-        <v>3374</v>
+        <v>6143</v>
       </c>
       <c r="D3" t="n">
-        <v>15792</v>
+        <v>14724</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3069</v>
+        <v>3097</v>
       </c>
       <c r="C4" t="n">
-        <v>3688</v>
+        <v>5968</v>
       </c>
       <c r="D4" t="n">
-        <v>7619</v>
+        <v>6349</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1901</v>
+        <v>1955</v>
       </c>
       <c r="C5" t="n">
-        <v>3974</v>
+        <v>5339</v>
       </c>
       <c r="D5" t="n">
-        <v>2561</v>
+        <v>2302</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1040</v>
+        <v>1081</v>
       </c>
       <c r="C6" t="n">
-        <v>3280</v>
+        <v>3397</v>
       </c>
       <c r="D6" t="n">
-        <v>1060</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>478</v>
+        <v>495</v>
       </c>
       <c r="C7" t="n">
-        <v>1876</v>
+        <v>1803</v>
       </c>
       <c r="D7" t="n">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C8" t="n">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="D8" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C9" t="n">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="D9" t="n">
         <v>310</v>
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -951,7 +951,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
         <v>100</v>
@@ -965,7 +965,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -979,7 +979,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
         <v>66</v>
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9346</v>
+        <v>6335</v>
       </c>
       <c r="C2" t="n">
-        <v>9036</v>
+        <v>6203</v>
       </c>
       <c r="D2" t="n">
-        <v>30510</v>
+        <v>30686</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4025</v>
+        <v>4074</v>
       </c>
       <c r="C3" t="n">
-        <v>3769</v>
+        <v>5956</v>
       </c>
       <c r="D3" t="n">
-        <v>16988</v>
+        <v>15965</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2884</v>
+        <v>3043</v>
       </c>
       <c r="C4" t="n">
-        <v>3425</v>
+        <v>5868</v>
       </c>
       <c r="D4" t="n">
-        <v>8648</v>
+        <v>7522</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2143</v>
+        <v>2157</v>
       </c>
       <c r="C5" t="n">
-        <v>3756</v>
+        <v>5517</v>
       </c>
       <c r="D5" t="n">
-        <v>3308</v>
+        <v>2831</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1280</v>
+        <v>1333</v>
       </c>
       <c r="C6" t="n">
-        <v>3528</v>
+        <v>4188</v>
       </c>
       <c r="D6" t="n">
-        <v>1265</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>643</v>
+        <v>662</v>
       </c>
       <c r="C7" t="n">
-        <v>2508</v>
+        <v>2487</v>
       </c>
       <c r="D7" t="n">
-        <v>697</v>
+        <v>682</v>
       </c>
     </row>
     <row r="8">
@@ -1178,10 +1178,10 @@
         <v>270</v>
       </c>
       <c r="C8" t="n">
-        <v>1241</v>
+        <v>1218</v>
       </c>
       <c r="D8" t="n">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9">
@@ -1192,10 +1192,10 @@
         <v>98</v>
       </c>
       <c r="C9" t="n">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="D9" t="n">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -1262,7 +1262,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
         <v>101</v>
@@ -1276,7 +1276,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -1290,7 +1290,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
         <v>66</v>
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8347</v>
+        <v>7968</v>
       </c>
       <c r="C2" t="n">
-        <v>10157</v>
+        <v>8587</v>
       </c>
       <c r="D2" t="n">
-        <v>38579</v>
+        <v>31556</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5042</v>
+        <v>4112</v>
       </c>
       <c r="C3" t="n">
-        <v>5279</v>
+        <v>5377</v>
       </c>
       <c r="D3" t="n">
-        <v>17604</v>
+        <v>16709</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2851</v>
+        <v>2943</v>
       </c>
       <c r="C4" t="n">
-        <v>3472</v>
+        <v>5727</v>
       </c>
       <c r="D4" t="n">
-        <v>9666</v>
+        <v>8436</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2176</v>
+        <v>2228</v>
       </c>
       <c r="C5" t="n">
-        <v>3534</v>
+        <v>5550</v>
       </c>
       <c r="D5" t="n">
-        <v>3944</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1481</v>
+        <v>1510</v>
       </c>
       <c r="C6" t="n">
-        <v>3555</v>
+        <v>4645</v>
       </c>
       <c r="D6" t="n">
-        <v>1542</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>806</v>
+        <v>828</v>
       </c>
       <c r="C7" t="n">
-        <v>2902</v>
+        <v>3145</v>
       </c>
       <c r="D7" t="n">
-        <v>760</v>
+        <v>747</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C8" t="n">
-        <v>1749</v>
+        <v>1714</v>
       </c>
       <c r="D8" t="n">
-        <v>481</v>
+        <v>476</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C9" t="n">
-        <v>786</v>
+        <v>767</v>
       </c>
       <c r="D9" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10">
@@ -1517,10 +1517,10 @@
         <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -1545,7 +1545,7 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D12" t="n">
         <v>165</v>
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1573,7 +1573,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
         <v>102</v>
@@ -1632,7 +1632,7 @@
         <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7761</v>
+        <v>7295</v>
       </c>
       <c r="C2" t="n">
-        <v>6825</v>
+        <v>5907</v>
       </c>
       <c r="D2" t="n">
-        <v>31539</v>
+        <v>26046</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5650</v>
+        <v>5099</v>
       </c>
       <c r="C3" t="n">
-        <v>7767</v>
+        <v>8487</v>
       </c>
       <c r="D3" t="n">
-        <v>19100</v>
+        <v>17830</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2010</v>
+        <v>2058</v>
       </c>
       <c r="C4" t="n">
-        <v>5325</v>
+        <v>8461</v>
       </c>
       <c r="D4" t="n">
-        <v>9090</v>
+        <v>7870</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1368</v>
+        <v>1395</v>
       </c>
       <c r="C5" t="n">
-        <v>3483</v>
+        <v>4552</v>
       </c>
       <c r="D5" t="n">
-        <v>2609</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>744</v>
+        <v>765</v>
       </c>
       <c r="C6" t="n">
-        <v>2843</v>
+        <v>3082</v>
       </c>
       <c r="D6" t="n">
-        <v>744</v>
+        <v>732</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C7" t="n">
-        <v>1714</v>
+        <v>1679</v>
       </c>
       <c r="D7" t="n">
-        <v>471</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>770</v>
+        <v>751</v>
       </c>
       <c r="D8" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9">
@@ -1814,10 +1814,10 @@
         <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D9" t="n">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11">
@@ -1842,7 +1842,7 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
         <v>161</v>
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13">
@@ -1870,7 +1870,7 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
         <v>99</v>
@@ -1929,7 +1929,7 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D20" t="n">
         <v>11</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4680</v>
+        <v>4580</v>
       </c>
       <c r="C2" t="n">
-        <v>3225</v>
+        <v>2725</v>
       </c>
       <c r="D2" t="n">
-        <v>22683</v>
+        <v>19067</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5674</v>
+        <v>5201</v>
       </c>
       <c r="C3" t="n">
-        <v>6641</v>
+        <v>6646</v>
       </c>
       <c r="D3" t="n">
-        <v>19691</v>
+        <v>18091</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2969</v>
+        <v>2792</v>
       </c>
       <c r="C4" t="n">
-        <v>6567</v>
+        <v>8540</v>
       </c>
       <c r="D4" t="n">
-        <v>10525</v>
+        <v>9140</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1515</v>
+        <v>1559</v>
       </c>
       <c r="C5" t="n">
-        <v>4338</v>
+        <v>6289</v>
       </c>
       <c r="D5" t="n">
-        <v>3388</v>
+        <v>2962</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>899</v>
+        <v>909</v>
       </c>
       <c r="C6" t="n">
-        <v>3209</v>
+        <v>3778</v>
       </c>
       <c r="D6" t="n">
-        <v>935</v>
+        <v>894</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C7" t="n">
-        <v>2174</v>
+        <v>2181</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>507</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C8" t="n">
-        <v>1033</v>
+        <v>1020</v>
       </c>
       <c r="D8" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9">
@@ -2125,10 +2125,10 @@
         <v>42</v>
       </c>
       <c r="C9" t="n">
-        <v>396</v>
+        <v>382</v>
       </c>
       <c r="D9" t="n">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2226,7 +2226,7 @@
         <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D19" t="n">
         <v>10</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5059</v>
+        <v>5602</v>
       </c>
       <c r="C2" t="n">
-        <v>6169</v>
+        <v>3435</v>
       </c>
       <c r="D2" t="n">
-        <v>22692</v>
+        <v>19859</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4413</v>
+        <v>4153</v>
       </c>
       <c r="C3" t="n">
-        <v>4401</v>
+        <v>4259</v>
       </c>
       <c r="D3" t="n">
-        <v>18956</v>
+        <v>17008</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3573</v>
+        <v>3267</v>
       </c>
       <c r="C4" t="n">
-        <v>6467</v>
+        <v>7435</v>
       </c>
       <c r="D4" t="n">
-        <v>11599</v>
+        <v>10322</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1882</v>
+        <v>1849</v>
       </c>
       <c r="C5" t="n">
-        <v>5359</v>
+        <v>7277</v>
       </c>
       <c r="D5" t="n">
-        <v>4449</v>
+        <v>3820</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1060</v>
+        <v>1089</v>
       </c>
       <c r="C6" t="n">
-        <v>3686</v>
+        <v>4850</v>
       </c>
       <c r="D6" t="n">
-        <v>1299</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="C7" t="n">
-        <v>2650</v>
+        <v>2890</v>
       </c>
       <c r="D7" t="n">
-        <v>574</v>
+        <v>554</v>
       </c>
     </row>
     <row r="8">
@@ -2422,7 +2422,7 @@
         <v>162</v>
       </c>
       <c r="C8" t="n">
-        <v>1512</v>
+        <v>1496</v>
       </c>
       <c r="D8" t="n">
         <v>358</v>
@@ -2433,10 +2433,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>643</v>
+        <v>623</v>
       </c>
       <c r="D9" t="n">
         <v>265</v>
@@ -2450,10 +2450,10 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3019</v>
+        <v>3307</v>
       </c>
       <c r="C2" t="n">
-        <v>2857</v>
+        <v>1652</v>
       </c>
       <c r="D2" t="n">
-        <v>15659</v>
+        <v>13904</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4407</v>
+        <v>4378</v>
       </c>
       <c r="C3" t="n">
-        <v>4868</v>
+        <v>3852</v>
       </c>
       <c r="D3" t="n">
-        <v>18919</v>
+        <v>16923</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3918</v>
+        <v>3585</v>
       </c>
       <c r="C4" t="n">
-        <v>6259</v>
+        <v>6957</v>
       </c>
       <c r="D4" t="n">
-        <v>12552</v>
+        <v>11118</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="C5" t="n">
-        <v>6444</v>
+        <v>8492</v>
       </c>
       <c r="D5" t="n">
-        <v>4813</v>
+        <v>4054</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="C6" t="n">
-        <v>4571</v>
+        <v>5751</v>
       </c>
       <c r="D6" t="n">
-        <v>1267</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="7">
@@ -2719,10 +2719,10 @@
         <v>149</v>
       </c>
       <c r="C7" t="n">
-        <v>2773</v>
+        <v>2909</v>
       </c>
       <c r="D7" t="n">
-        <v>578</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>1104</v>
+        <v>1065</v>
       </c>
       <c r="D8" t="n">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D18" t="n">
         <v>6</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4730</v>
+        <v>3759</v>
       </c>
       <c r="C2" t="n">
-        <v>7351</v>
+        <v>9137</v>
       </c>
       <c r="D2" t="n">
-        <v>18918</v>
+        <v>19779</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3267</v>
+        <v>3360</v>
       </c>
       <c r="C3" t="n">
-        <v>3502</v>
+        <v>2546</v>
       </c>
       <c r="D3" t="n">
-        <v>17204</v>
+        <v>15537</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3638</v>
+        <v>3409</v>
       </c>
       <c r="C4" t="n">
-        <v>5521</v>
+        <v>5351</v>
       </c>
       <c r="D4" t="n">
-        <v>13209</v>
+        <v>11671</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2413</v>
+        <v>2312</v>
       </c>
       <c r="C5" t="n">
-        <v>6226</v>
+        <v>7704</v>
       </c>
       <c r="D5" t="n">
-        <v>5901</v>
+        <v>4947</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1160</v>
+        <v>1168</v>
       </c>
       <c r="C6" t="n">
-        <v>5426</v>
+        <v>6912</v>
       </c>
       <c r="D6" t="n">
-        <v>1727</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="C7" t="n">
-        <v>3521</v>
+        <v>4106</v>
       </c>
       <c r="D7" t="n">
-        <v>665</v>
+        <v>637</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>1757</v>
+        <v>1754</v>
       </c>
       <c r="D8" t="n">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>553</v>
+        <v>537</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3103,7 +3103,7 @@
         <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3251</v>
+        <v>2720</v>
       </c>
       <c r="C2" t="n">
-        <v>3966</v>
+        <v>5048</v>
       </c>
       <c r="D2" t="n">
-        <v>13780</v>
+        <v>14383</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3282</v>
+        <v>3056</v>
       </c>
       <c r="C3" t="n">
-        <v>4562</v>
+        <v>4706</v>
       </c>
       <c r="D3" t="n">
-        <v>16473</v>
+        <v>15200</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3249</v>
+        <v>3124</v>
       </c>
       <c r="C4" t="n">
-        <v>4731</v>
+        <v>4262</v>
       </c>
       <c r="D4" t="n">
-        <v>13471</v>
+        <v>12059</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2652</v>
+        <v>2497</v>
       </c>
       <c r="C5" t="n">
-        <v>6018</v>
+        <v>6929</v>
       </c>
       <c r="D5" t="n">
-        <v>6676</v>
+        <v>5554</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1372</v>
+        <v>1381</v>
       </c>
       <c r="C6" t="n">
-        <v>5960</v>
+        <v>7446</v>
       </c>
       <c r="D6" t="n">
-        <v>2100</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>316</v>
+        <v>296</v>
       </c>
       <c r="C7" t="n">
-        <v>4193</v>
+        <v>5073</v>
       </c>
       <c r="D7" t="n">
-        <v>754</v>
+        <v>705</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>2244</v>
+        <v>2320</v>
       </c>
       <c r="D8" t="n">
-        <v>415</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>651</v>
+        <v>614</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
         <v>136</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4454</v>
+        <v>4854</v>
       </c>
       <c r="C2" t="n">
-        <v>9634</v>
+        <v>8713</v>
       </c>
       <c r="D2" t="n">
-        <v>16695</v>
+        <v>13963</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2751</v>
+        <v>2471</v>
       </c>
       <c r="C3" t="n">
-        <v>3836</v>
+        <v>4306</v>
       </c>
       <c r="D3" t="n">
-        <v>15095</v>
+        <v>14129</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2833</v>
+        <v>2720</v>
       </c>
       <c r="C4" t="n">
-        <v>4559</v>
+        <v>4360</v>
       </c>
       <c r="D4" t="n">
-        <v>13493</v>
+        <v>12144</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2607</v>
+        <v>2470</v>
       </c>
       <c r="C5" t="n">
-        <v>5361</v>
+        <v>5709</v>
       </c>
       <c r="D5" t="n">
-        <v>7322</v>
+        <v>6259</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1684</v>
+        <v>1633</v>
       </c>
       <c r="C6" t="n">
-        <v>5931</v>
+        <v>7184</v>
       </c>
       <c r="D6" t="n">
-        <v>2687</v>
+        <v>2295</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>583</v>
+        <v>562</v>
       </c>
       <c r="C7" t="n">
-        <v>4907</v>
+        <v>5954</v>
       </c>
       <c r="D7" t="n">
-        <v>917</v>
+        <v>833</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C8" t="n">
-        <v>2930</v>
+        <v>3313</v>
       </c>
       <c r="D8" t="n">
-        <v>450</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>1187</v>
+        <v>1171</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>357</v>
+        <v>337</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
+        <v>92</v>
+      </c>
+      <c r="D12" t="n">
         <v>94</v>
-      </c>
-      <c r="D12" t="n">
-        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4932</v>
+        <v>4820</v>
       </c>
       <c r="C2" t="n">
-        <v>4520</v>
+        <v>4279</v>
       </c>
       <c r="D2" t="n">
-        <v>4941</v>
+        <v>3787</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3188</v>
+        <v>3470</v>
       </c>
       <c r="C2" t="n">
-        <v>5472</v>
+        <v>5019</v>
       </c>
       <c r="D2" t="n">
-        <v>12287</v>
+        <v>10276</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3628</v>
+        <v>3413</v>
       </c>
       <c r="C3" t="n">
-        <v>5512</v>
+        <v>5672</v>
       </c>
       <c r="D3" t="n">
-        <v>16466</v>
+        <v>15273</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3857</v>
+        <v>3650</v>
       </c>
       <c r="C4" t="n">
-        <v>6428</v>
+        <v>6407</v>
       </c>
       <c r="D4" t="n">
-        <v>13733</v>
+        <v>12344</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1628</v>
+        <v>1577</v>
       </c>
       <c r="C5" t="n">
-        <v>8091</v>
+        <v>9304</v>
       </c>
       <c r="D5" t="n">
-        <v>6658</v>
+        <v>5631</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>538</v>
+        <v>519</v>
       </c>
       <c r="C6" t="n">
-        <v>6029</v>
+        <v>7242</v>
       </c>
       <c r="D6" t="n">
-        <v>2098</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C7" t="n">
-        <v>2871</v>
+        <v>3246</v>
       </c>
       <c r="D7" t="n">
-        <v>557</v>
+        <v>533</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>1163</v>
+        <v>1147</v>
       </c>
       <c r="D8" t="n">
-        <v>303</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>349</v>
+        <v>330</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
+        <v>90</v>
+      </c>
+      <c r="D11" t="n">
         <v>92</v>
-      </c>
-      <c r="D11" t="n">
-        <v>93</v>
       </c>
     </row>
     <row r="12">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7050</v>
+        <v>6985</v>
       </c>
       <c r="C2" t="n">
-        <v>5860</v>
+        <v>7553</v>
       </c>
       <c r="D2" t="n">
-        <v>11270</v>
+        <v>14085</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2096</v>
+        <v>2049</v>
       </c>
       <c r="C3" t="n">
-        <v>2314</v>
+        <v>2190</v>
       </c>
       <c r="D3" t="n">
-        <v>1508</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="4">
@@ -4546,7 +4546,7 @@
         <v>114</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="5">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5254</v>
+        <v>6134</v>
       </c>
       <c r="C2" t="n">
-        <v>9751</v>
+        <v>5956</v>
       </c>
       <c r="D2" t="n">
-        <v>19224</v>
+        <v>14116</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3751</v>
+        <v>3705</v>
       </c>
       <c r="C3" t="n">
-        <v>3750</v>
+        <v>4545</v>
       </c>
       <c r="D3" t="n">
-        <v>3037</v>
+        <v>3349</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>944</v>
+        <v>923</v>
       </c>
       <c r="C4" t="n">
-        <v>1421</v>
+        <v>1347</v>
       </c>
       <c r="D4" t="n">
-        <v>1485</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="5">
@@ -4871,7 +4871,7 @@
         <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="6">
@@ -4910,7 +4910,7 @@
         <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
         <v>441</v>
@@ -4924,7 +4924,7 @@
         <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5099</v>
+        <v>5114</v>
       </c>
       <c r="C2" t="n">
-        <v>7584</v>
+        <v>10109</v>
       </c>
       <c r="D2" t="n">
-        <v>25956</v>
+        <v>20913</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3689</v>
+        <v>4063</v>
       </c>
       <c r="C3" t="n">
-        <v>6078</v>
+        <v>4600</v>
       </c>
       <c r="D3" t="n">
-        <v>5408</v>
+        <v>4830</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1984</v>
+        <v>1955</v>
       </c>
       <c r="C4" t="n">
-        <v>2696</v>
+        <v>3117</v>
       </c>
       <c r="D4" t="n">
-        <v>1737</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="C5" t="n">
-        <v>884</v>
+        <v>842</v>
       </c>
       <c r="D5" t="n">
-        <v>1193</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="6">
@@ -5196,7 +5196,7 @@
         <v>303</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>911</v>
       </c>
     </row>
     <row r="7">
@@ -5221,7 +5221,7 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D8" t="n">
         <v>462</v>
@@ -5235,7 +5235,7 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
         <v>372</v>
@@ -5249,7 +5249,7 @@
         <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5347,10 +5347,10 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5621</v>
+        <v>6203</v>
       </c>
       <c r="C2" t="n">
-        <v>6510</v>
+        <v>8065</v>
       </c>
       <c r="D2" t="n">
-        <v>29323</v>
+        <v>24125</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3583</v>
+        <v>3757</v>
       </c>
       <c r="C3" t="n">
-        <v>5964</v>
+        <v>6508</v>
       </c>
       <c r="D3" t="n">
-        <v>8150</v>
+        <v>6934</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2390</v>
+        <v>2526</v>
       </c>
       <c r="C4" t="n">
-        <v>4432</v>
+        <v>3863</v>
       </c>
       <c r="D4" t="n">
-        <v>2337</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1009</v>
+        <v>993</v>
       </c>
       <c r="C5" t="n">
-        <v>1822</v>
+        <v>2025</v>
       </c>
       <c r="D5" t="n">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="6">
@@ -5501,10 +5501,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>595</v>
+        <v>570</v>
       </c>
       <c r="D6" t="n">
         <v>946</v>
@@ -5518,10 +5518,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
@@ -5532,7 +5532,7 @@
         <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D8" t="n">
         <v>484</v>
@@ -5560,7 +5560,7 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5577,7 +5577,7 @@
         <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12">
@@ -5591,7 +5591,7 @@
         <v>160</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5675,7 +5675,7 @@
         <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
@@ -5686,10 +5686,10 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7705</v>
+        <v>6719</v>
       </c>
       <c r="C2" t="n">
-        <v>4254</v>
+        <v>10798</v>
       </c>
       <c r="D2" t="n">
-        <v>37094</v>
+        <v>27570</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3323</v>
+        <v>3640</v>
       </c>
       <c r="C3" t="n">
-        <v>5114</v>
+        <v>5983</v>
       </c>
       <c r="D3" t="n">
-        <v>10154</v>
+        <v>8522</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1841</v>
+        <v>1937</v>
       </c>
       <c r="C4" t="n">
-        <v>4289</v>
+        <v>4330</v>
       </c>
       <c r="D4" t="n">
-        <v>2884</v>
+        <v>2634</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>882</v>
+        <v>910</v>
       </c>
       <c r="C5" t="n">
-        <v>2344</v>
+        <v>2191</v>
       </c>
       <c r="D5" t="n">
-        <v>1146</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="6">
@@ -5812,10 +5812,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="C6" t="n">
-        <v>813</v>
+        <v>874</v>
       </c>
       <c r="D6" t="n">
         <v>760</v>
@@ -5829,10 +5829,10 @@
         <v>88</v>
       </c>
       <c r="C7" t="n">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="D7" t="n">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="8">
@@ -5854,7 +5854,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
         <v>198</v>
@@ -5888,7 +5888,7 @@
         <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
@@ -5972,7 +5972,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6000,7 +6000,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5803</v>
+        <v>6684</v>
       </c>
       <c r="C2" t="n">
-        <v>3897</v>
+        <v>6129</v>
       </c>
       <c r="D2" t="n">
-        <v>30310</v>
+        <v>30289</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4597</v>
+        <v>4306</v>
       </c>
       <c r="C3" t="n">
-        <v>3994</v>
+        <v>7596</v>
       </c>
       <c r="D3" t="n">
-        <v>14229</v>
+        <v>11233</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2269</v>
+        <v>2452</v>
       </c>
       <c r="C4" t="n">
-        <v>4657</v>
+        <v>5255</v>
       </c>
       <c r="D4" t="n">
-        <v>4234</v>
+        <v>3797</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1207</v>
+        <v>1262</v>
       </c>
       <c r="C5" t="n">
-        <v>3452</v>
+        <v>3418</v>
       </c>
       <c r="D5" t="n">
-        <v>1461</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>552</v>
+        <v>563</v>
       </c>
       <c r="C6" t="n">
-        <v>1684</v>
+        <v>1621</v>
       </c>
       <c r="D6" t="n">
-        <v>815</v>
+        <v>813</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C7" t="n">
-        <v>592</v>
+        <v>623</v>
       </c>
       <c r="D7" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8">
@@ -6154,10 +6154,10 @@
         <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="D8" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
         <v>152</v>
@@ -6283,7 +6283,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4847</v>
+        <v>5767</v>
       </c>
       <c r="C2" t="n">
-        <v>4320</v>
+        <v>8209</v>
       </c>
       <c r="D2" t="n">
-        <v>23183</v>
+        <v>28603</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4272</v>
+        <v>4491</v>
       </c>
       <c r="C3" t="n">
-        <v>3411</v>
+        <v>5882</v>
       </c>
       <c r="D3" t="n">
-        <v>15777</v>
+        <v>13473</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2924</v>
+        <v>2884</v>
       </c>
       <c r="C4" t="n">
-        <v>4184</v>
+        <v>6471</v>
       </c>
       <c r="D4" t="n">
-        <v>6024</v>
+        <v>5109</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1530</v>
+        <v>1632</v>
       </c>
       <c r="C5" t="n">
-        <v>4006</v>
+        <v>4352</v>
       </c>
       <c r="D5" t="n">
-        <v>1908</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>793</v>
+        <v>822</v>
       </c>
       <c r="C6" t="n">
-        <v>2614</v>
+        <v>2535</v>
       </c>
       <c r="D6" t="n">
-        <v>921</v>
+        <v>909</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="C7" t="n">
-        <v>1169</v>
+        <v>1150</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="8">
@@ -6465,10 +6465,10 @@
         <v>105</v>
       </c>
       <c r="C8" t="n">
-        <v>432</v>
+        <v>445</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="9">
@@ -6493,7 +6493,7 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
         <v>241</v>
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6535,7 +6535,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
         <v>122</v>
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">

--- a/output/yearly_population_iteration_50_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_50_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6017</v>
+        <v>4518</v>
       </c>
       <c r="C2" t="n">
-        <v>7522</v>
+        <v>8477</v>
       </c>
       <c r="D2" t="n">
-        <v>31125</v>
+        <v>27571</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4180</v>
+        <v>3234</v>
       </c>
       <c r="C3" t="n">
-        <v>6143</v>
+        <v>4120</v>
       </c>
       <c r="D3" t="n">
-        <v>14724</v>
+        <v>10741</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3097</v>
+        <v>2488</v>
       </c>
       <c r="C4" t="n">
-        <v>5968</v>
+        <v>4894</v>
       </c>
       <c r="D4" t="n">
-        <v>6349</v>
+        <v>5996</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1955</v>
+        <v>1570</v>
       </c>
       <c r="C5" t="n">
-        <v>5339</v>
+        <v>4211</v>
       </c>
       <c r="D5" t="n">
-        <v>2302</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1081</v>
+        <v>908</v>
       </c>
       <c r="C6" t="n">
-        <v>3397</v>
+        <v>3605</v>
       </c>
       <c r="D6" t="n">
-        <v>1030</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>495</v>
+        <v>415</v>
       </c>
       <c r="C7" t="n">
-        <v>1803</v>
+        <v>2465</v>
       </c>
       <c r="D7" t="n">
-        <v>637</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>177</v>
+        <v>152</v>
       </c>
       <c r="C8" t="n">
-        <v>776</v>
+        <v>1234</v>
       </c>
       <c r="D8" t="n">
-        <v>432</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C9" t="n">
-        <v>329</v>
+        <v>495</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>206</v>
+        <v>229</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -926,7 +926,7 @@
         <v>127</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
         <v>123</v>
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1010,7 +1010,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1052,7 +1052,7 @@
         <v>98</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6335</v>
+        <v>4910</v>
       </c>
       <c r="C2" t="n">
-        <v>6203</v>
+        <v>5565</v>
       </c>
       <c r="D2" t="n">
-        <v>30686</v>
+        <v>26188</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4074</v>
+        <v>3107</v>
       </c>
       <c r="C3" t="n">
-        <v>5956</v>
+        <v>5340</v>
       </c>
       <c r="D3" t="n">
-        <v>15965</v>
+        <v>12308</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3043</v>
+        <v>2401</v>
       </c>
       <c r="C4" t="n">
-        <v>5868</v>
+        <v>4381</v>
       </c>
       <c r="D4" t="n">
-        <v>7522</v>
+        <v>6588</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2157</v>
+        <v>1732</v>
       </c>
       <c r="C5" t="n">
-        <v>5517</v>
+        <v>4438</v>
       </c>
       <c r="D5" t="n">
-        <v>2831</v>
+        <v>3018</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1333</v>
+        <v>1094</v>
       </c>
       <c r="C6" t="n">
-        <v>4188</v>
+        <v>3802</v>
       </c>
       <c r="D6" t="n">
-        <v>1211</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>662</v>
+        <v>555</v>
       </c>
       <c r="C7" t="n">
-        <v>2487</v>
+        <v>2966</v>
       </c>
       <c r="D7" t="n">
-        <v>682</v>
+        <v>718</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>270</v>
+        <v>229</v>
       </c>
       <c r="C8" t="n">
-        <v>1218</v>
+        <v>1740</v>
       </c>
       <c r="D8" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="C9" t="n">
-        <v>509</v>
+        <v>794</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C10" t="n">
-        <v>255</v>
+        <v>335</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1262,7 +1262,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
         <v>101</v>
@@ -1279,7 +1279,7 @@
         <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1363,7 +1363,7 @@
         <v>104</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7968</v>
+        <v>6277</v>
       </c>
       <c r="C2" t="n">
-        <v>8587</v>
+        <v>7044</v>
       </c>
       <c r="D2" t="n">
-        <v>31556</v>
+        <v>35744</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4112</v>
+        <v>3133</v>
       </c>
       <c r="C3" t="n">
-        <v>5377</v>
+        <v>4822</v>
       </c>
       <c r="D3" t="n">
-        <v>16709</v>
+        <v>13185</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2943</v>
+        <v>2294</v>
       </c>
       <c r="C4" t="n">
-        <v>5727</v>
+        <v>4662</v>
       </c>
       <c r="D4" t="n">
-        <v>8436</v>
+        <v>7148</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2228</v>
+        <v>1797</v>
       </c>
       <c r="C5" t="n">
-        <v>5550</v>
+        <v>4279</v>
       </c>
       <c r="D5" t="n">
-        <v>3420</v>
+        <v>3440</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1510</v>
+        <v>1227</v>
       </c>
       <c r="C6" t="n">
-        <v>4645</v>
+        <v>4030</v>
       </c>
       <c r="D6" t="n">
-        <v>1401</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>828</v>
+        <v>687</v>
       </c>
       <c r="C7" t="n">
-        <v>3145</v>
+        <v>3271</v>
       </c>
       <c r="D7" t="n">
-        <v>747</v>
+        <v>791</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>373</v>
+        <v>313</v>
       </c>
       <c r="C8" t="n">
-        <v>1714</v>
+        <v>2219</v>
       </c>
       <c r="D8" t="n">
-        <v>476</v>
+        <v>489</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="C9" t="n">
-        <v>767</v>
+        <v>1138</v>
       </c>
       <c r="D9" t="n">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10">
@@ -1514,10 +1514,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>346</v>
+        <v>498</v>
       </c>
       <c r="D10" t="n">
         <v>254</v>
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>203</v>
+        <v>239</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1604,7 @@
         <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1674,7 +1674,7 @@
         <v>110</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7295</v>
+        <v>5722</v>
       </c>
       <c r="C2" t="n">
-        <v>5907</v>
+        <v>4789</v>
       </c>
       <c r="D2" t="n">
-        <v>26046</v>
+        <v>29228</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5099</v>
+        <v>3929</v>
       </c>
       <c r="C3" t="n">
-        <v>8487</v>
+        <v>7398</v>
       </c>
       <c r="D3" t="n">
-        <v>17830</v>
+        <v>14220</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2058</v>
+        <v>1660</v>
       </c>
       <c r="C4" t="n">
-        <v>8461</v>
+        <v>6658</v>
       </c>
       <c r="D4" t="n">
-        <v>7870</v>
+        <v>7043</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1395</v>
+        <v>1133</v>
       </c>
       <c r="C5" t="n">
-        <v>4552</v>
+        <v>3949</v>
       </c>
       <c r="D5" t="n">
-        <v>2292</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>765</v>
+        <v>634</v>
       </c>
       <c r="C6" t="n">
-        <v>3082</v>
+        <v>3205</v>
       </c>
       <c r="D6" t="n">
-        <v>732</v>
+        <v>775</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>344</v>
+        <v>289</v>
       </c>
       <c r="C7" t="n">
-        <v>1679</v>
+        <v>2174</v>
       </c>
       <c r="D7" t="n">
-        <v>466</v>
+        <v>479</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="C8" t="n">
-        <v>751</v>
+        <v>1115</v>
       </c>
       <c r="D8" t="n">
-        <v>327</v>
+        <v>320</v>
       </c>
     </row>
     <row r="9">
@@ -1811,10 +1811,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>339</v>
+        <v>488</v>
       </c>
       <c r="D9" t="n">
         <v>248</v>
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>198</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -1971,7 +1971,7 @@
         <v>110</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4580</v>
+        <v>3526</v>
       </c>
       <c r="C2" t="n">
-        <v>2725</v>
+        <v>2228</v>
       </c>
       <c r="D2" t="n">
-        <v>19067</v>
+        <v>20314</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5201</v>
+        <v>4040</v>
       </c>
       <c r="C3" t="n">
-        <v>6646</v>
+        <v>5646</v>
       </c>
       <c r="D3" t="n">
-        <v>18091</v>
+        <v>15442</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2792</v>
+        <v>2198</v>
       </c>
       <c r="C4" t="n">
-        <v>8540</v>
+        <v>7052</v>
       </c>
       <c r="D4" t="n">
-        <v>9140</v>
+        <v>8066</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1559</v>
+        <v>1264</v>
       </c>
       <c r="C5" t="n">
-        <v>6289</v>
+        <v>5174</v>
       </c>
       <c r="D5" t="n">
-        <v>2962</v>
+        <v>2988</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>909</v>
+        <v>751</v>
       </c>
       <c r="C6" t="n">
-        <v>3778</v>
+        <v>3657</v>
       </c>
       <c r="D6" t="n">
-        <v>894</v>
+        <v>948</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>323</v>
+        <v>273</v>
       </c>
       <c r="C7" t="n">
-        <v>2181</v>
+        <v>2616</v>
       </c>
       <c r="D7" t="n">
-        <v>507</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="C8" t="n">
-        <v>1020</v>
+        <v>1460</v>
       </c>
       <c r="D8" t="n">
-        <v>341</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9">
@@ -2122,10 +2122,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C9" t="n">
-        <v>382</v>
+        <v>536</v>
       </c>
       <c r="D9" t="n">
         <v>256</v>
@@ -2139,7 +2139,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>245</v>
       </c>
       <c r="D10" t="n">
         <v>209</v>
@@ -2153,10 +2153,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2170,7 +2170,7 @@
         <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2268,7 +2268,7 @@
         <v>107</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5602</v>
+        <v>3477</v>
       </c>
       <c r="C2" t="n">
-        <v>3435</v>
+        <v>8751</v>
       </c>
       <c r="D2" t="n">
-        <v>19859</v>
+        <v>21022</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4153</v>
+        <v>3209</v>
       </c>
       <c r="C3" t="n">
-        <v>4259</v>
+        <v>3528</v>
       </c>
       <c r="D3" t="n">
-        <v>17008</v>
+        <v>15229</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3267</v>
+        <v>2588</v>
       </c>
       <c r="C4" t="n">
-        <v>7435</v>
+        <v>6271</v>
       </c>
       <c r="D4" t="n">
-        <v>10322</v>
+        <v>9024</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1849</v>
+        <v>1477</v>
       </c>
       <c r="C5" t="n">
-        <v>7277</v>
+        <v>5949</v>
       </c>
       <c r="D5" t="n">
-        <v>3820</v>
+        <v>3648</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1089</v>
+        <v>885</v>
       </c>
       <c r="C6" t="n">
-        <v>4850</v>
+        <v>4341</v>
       </c>
       <c r="D6" t="n">
-        <v>1179</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>480</v>
+        <v>408</v>
       </c>
       <c r="C7" t="n">
-        <v>2890</v>
+        <v>3063</v>
       </c>
       <c r="D7" t="n">
-        <v>554</v>
+        <v>575</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>162</v>
+        <v>139</v>
       </c>
       <c r="C8" t="n">
-        <v>1496</v>
+        <v>1949</v>
       </c>
       <c r="D8" t="n">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>623</v>
+        <v>899</v>
       </c>
       <c r="D9" t="n">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>279</v>
+        <v>347</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2481,7 +2481,7 @@
         <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3307</v>
+        <v>2063</v>
       </c>
       <c r="C2" t="n">
-        <v>1652</v>
+        <v>4016</v>
       </c>
       <c r="D2" t="n">
-        <v>13904</v>
+        <v>14489</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4378</v>
+        <v>3157</v>
       </c>
       <c r="C3" t="n">
-        <v>3852</v>
+        <v>5211</v>
       </c>
       <c r="D3" t="n">
-        <v>16923</v>
+        <v>15512</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3585</v>
+        <v>2860</v>
       </c>
       <c r="C4" t="n">
-        <v>6957</v>
+        <v>5881</v>
       </c>
       <c r="D4" t="n">
-        <v>11118</v>
+        <v>9900</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1930</v>
+        <v>1549</v>
       </c>
       <c r="C5" t="n">
-        <v>8492</v>
+        <v>6905</v>
       </c>
       <c r="D5" t="n">
-        <v>4054</v>
+        <v>3862</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>886</v>
+        <v>736</v>
       </c>
       <c r="C6" t="n">
-        <v>5751</v>
+        <v>5344</v>
       </c>
       <c r="D6" t="n">
-        <v>1164</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="C7" t="n">
-        <v>2909</v>
+        <v>3339</v>
       </c>
       <c r="D7" t="n">
-        <v>561</v>
+        <v>575</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C8" t="n">
-        <v>1065</v>
+        <v>1492</v>
       </c>
       <c r="D8" t="n">
-        <v>378</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>273</v>
+        <v>340</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2778,7 +2778,7 @@
         <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -2806,7 +2806,7 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
         <v>35</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3759</v>
+        <v>2186</v>
       </c>
       <c r="C2" t="n">
-        <v>9137</v>
+        <v>5223</v>
       </c>
       <c r="D2" t="n">
-        <v>19779</v>
+        <v>12853</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3360</v>
+        <v>2307</v>
       </c>
       <c r="C3" t="n">
-        <v>2546</v>
+        <v>4139</v>
       </c>
       <c r="D3" t="n">
-        <v>15537</v>
+        <v>14330</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3409</v>
+        <v>2635</v>
       </c>
       <c r="C4" t="n">
-        <v>5351</v>
+        <v>5493</v>
       </c>
       <c r="D4" t="n">
-        <v>11671</v>
+        <v>10514</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2312</v>
+        <v>1850</v>
       </c>
       <c r="C5" t="n">
-        <v>7704</v>
+        <v>6299</v>
       </c>
       <c r="D5" t="n">
-        <v>4947</v>
+        <v>4709</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1168</v>
+        <v>947</v>
       </c>
       <c r="C6" t="n">
-        <v>6912</v>
+        <v>6072</v>
       </c>
       <c r="D6" t="n">
-        <v>1537</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>329</v>
+        <v>282</v>
       </c>
       <c r="C7" t="n">
-        <v>4106</v>
+        <v>4175</v>
       </c>
       <c r="D7" t="n">
-        <v>637</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C8" t="n">
-        <v>1754</v>
+        <v>2223</v>
       </c>
       <c r="D8" t="n">
-        <v>397</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>537</v>
+        <v>719</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>240</v>
       </c>
       <c r="D10" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D12" t="n">
         <v>99</v>
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
         <v>34</v>
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2720</v>
+        <v>1544</v>
       </c>
       <c r="C2" t="n">
-        <v>5048</v>
+        <v>3937</v>
       </c>
       <c r="D2" t="n">
-        <v>14383</v>
+        <v>9180</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3056</v>
+        <v>1985</v>
       </c>
       <c r="C3" t="n">
-        <v>4706</v>
+        <v>4186</v>
       </c>
       <c r="D3" t="n">
-        <v>15200</v>
+        <v>13373</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3124</v>
+        <v>2337</v>
       </c>
       <c r="C4" t="n">
-        <v>4262</v>
+        <v>4978</v>
       </c>
       <c r="D4" t="n">
-        <v>12059</v>
+        <v>10808</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2497</v>
+        <v>1986</v>
       </c>
       <c r="C5" t="n">
-        <v>6929</v>
+        <v>6055</v>
       </c>
       <c r="D5" t="n">
-        <v>5554</v>
+        <v>5324</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1381</v>
+        <v>1123</v>
       </c>
       <c r="C6" t="n">
-        <v>7446</v>
+        <v>6398</v>
       </c>
       <c r="D6" t="n">
-        <v>1858</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>296</v>
+        <v>265</v>
       </c>
       <c r="C7" t="n">
-        <v>5073</v>
+        <v>4943</v>
       </c>
       <c r="D7" t="n">
-        <v>705</v>
+        <v>733</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>2320</v>
+        <v>2771</v>
       </c>
       <c r="D8" t="n">
-        <v>409</v>
+        <v>414</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>614</v>
+        <v>856</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="D10" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
         <v>37</v>
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4854</v>
+        <v>2746</v>
       </c>
       <c r="C2" t="n">
-        <v>8713</v>
+        <v>6769</v>
       </c>
       <c r="D2" t="n">
-        <v>13963</v>
+        <v>10607</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2471</v>
+        <v>1534</v>
       </c>
       <c r="C3" t="n">
-        <v>4306</v>
+        <v>3659</v>
       </c>
       <c r="D3" t="n">
-        <v>14129</v>
+        <v>12013</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2720</v>
+        <v>1939</v>
       </c>
       <c r="C4" t="n">
-        <v>4360</v>
+        <v>4532</v>
       </c>
       <c r="D4" t="n">
-        <v>12144</v>
+        <v>10848</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2470</v>
+        <v>1924</v>
       </c>
       <c r="C5" t="n">
-        <v>5709</v>
+        <v>5484</v>
       </c>
       <c r="D5" t="n">
-        <v>6259</v>
+        <v>5848</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1633</v>
+        <v>1323</v>
       </c>
       <c r="C6" t="n">
-        <v>7184</v>
+        <v>6207</v>
       </c>
       <c r="D6" t="n">
-        <v>2295</v>
+        <v>2297</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>562</v>
+        <v>482</v>
       </c>
       <c r="C7" t="n">
-        <v>5954</v>
+        <v>5497</v>
       </c>
       <c r="D7" t="n">
-        <v>833</v>
+        <v>868</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C8" t="n">
-        <v>3313</v>
+        <v>3584</v>
       </c>
       <c r="D8" t="n">
-        <v>436</v>
+        <v>447</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>1171</v>
+        <v>1502</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>303</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>337</v>
+        <v>431</v>
       </c>
       <c r="D10" t="n">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3739,7 +3739,7 @@
         <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
         <v>38</v>
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4820</v>
+        <v>4418</v>
       </c>
       <c r="C2" t="n">
-        <v>4279</v>
+        <v>13308</v>
       </c>
       <c r="D2" t="n">
-        <v>3787</v>
+        <v>10561</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3470</v>
+        <v>1942</v>
       </c>
       <c r="C2" t="n">
-        <v>5019</v>
+        <v>3791</v>
       </c>
       <c r="D2" t="n">
-        <v>10276</v>
+        <v>7806</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3413</v>
+        <v>2181</v>
       </c>
       <c r="C3" t="n">
-        <v>5672</v>
+        <v>4715</v>
       </c>
       <c r="D3" t="n">
-        <v>15273</v>
+        <v>12940</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3650</v>
+        <v>2747</v>
       </c>
       <c r="C4" t="n">
-        <v>6407</v>
+        <v>6404</v>
       </c>
       <c r="D4" t="n">
-        <v>12344</v>
+        <v>11032</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1577</v>
+        <v>1293</v>
       </c>
       <c r="C5" t="n">
-        <v>9304</v>
+        <v>8438</v>
       </c>
       <c r="D5" t="n">
-        <v>5631</v>
+        <v>5392</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>519</v>
+        <v>445</v>
       </c>
       <c r="C6" t="n">
-        <v>7242</v>
+        <v>6664</v>
       </c>
       <c r="D6" t="n">
-        <v>1834</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C7" t="n">
-        <v>3246</v>
+        <v>3512</v>
       </c>
       <c r="D7" t="n">
-        <v>533</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>1147</v>
+        <v>1471</v>
       </c>
       <c r="D8" t="n">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>330</v>
+        <v>422</v>
       </c>
       <c r="D9" t="n">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>50</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
         <v>37</v>
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6985</v>
+        <v>6097</v>
       </c>
       <c r="C2" t="n">
-        <v>7553</v>
+        <v>6759</v>
       </c>
       <c r="D2" t="n">
-        <v>14085</v>
+        <v>14351</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2049</v>
+        <v>1878</v>
       </c>
       <c r="C3" t="n">
-        <v>2190</v>
+        <v>6707</v>
       </c>
       <c r="D3" t="n">
-        <v>1297</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="4">
@@ -4543,10 +4543,10 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
-        <v>1546</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="5">
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6134</v>
+        <v>4335</v>
       </c>
       <c r="C2" t="n">
-        <v>5956</v>
+        <v>6890</v>
       </c>
       <c r="D2" t="n">
-        <v>14116</v>
+        <v>25082</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3705</v>
+        <v>3271</v>
       </c>
       <c r="C3" t="n">
-        <v>4545</v>
+        <v>5809</v>
       </c>
       <c r="D3" t="n">
-        <v>3349</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>923</v>
+        <v>850</v>
       </c>
       <c r="C4" t="n">
-        <v>1347</v>
+        <v>3973</v>
       </c>
       <c r="D4" t="n">
-        <v>1448</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D5" t="n">
-        <v>1188</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5114</v>
+        <v>5518</v>
       </c>
       <c r="C2" t="n">
-        <v>10109</v>
+        <v>7704</v>
       </c>
       <c r="D2" t="n">
-        <v>20913</v>
+        <v>20124</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4063</v>
+        <v>3148</v>
       </c>
       <c r="C3" t="n">
-        <v>4600</v>
+        <v>5539</v>
       </c>
       <c r="D3" t="n">
-        <v>4830</v>
+        <v>7269</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1955</v>
+        <v>1721</v>
       </c>
       <c r="C4" t="n">
-        <v>3117</v>
+        <v>4874</v>
       </c>
       <c r="D4" t="n">
-        <v>1768</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>439</v>
+        <v>403</v>
       </c>
       <c r="C5" t="n">
-        <v>842</v>
+        <v>2271</v>
       </c>
       <c r="D5" t="n">
-        <v>1187</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D6" t="n">
-        <v>911</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5288,10 +5288,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5361,10 +5361,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19">
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6203</v>
+        <v>4874</v>
       </c>
       <c r="C2" t="n">
-        <v>8065</v>
+        <v>6021</v>
       </c>
       <c r="D2" t="n">
-        <v>24125</v>
+        <v>19094</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3757</v>
+        <v>3478</v>
       </c>
       <c r="C3" t="n">
-        <v>6508</v>
+        <v>5782</v>
       </c>
       <c r="D3" t="n">
-        <v>6934</v>
+        <v>8711</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2526</v>
+        <v>2040</v>
       </c>
       <c r="C4" t="n">
-        <v>3863</v>
+        <v>5076</v>
       </c>
       <c r="D4" t="n">
-        <v>2255</v>
+        <v>2986</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>993</v>
+        <v>872</v>
       </c>
       <c r="C5" t="n">
-        <v>2025</v>
+        <v>3573</v>
       </c>
       <c r="D5" t="n">
-        <v>1256</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="C6" t="n">
-        <v>570</v>
+        <v>1283</v>
       </c>
       <c r="D6" t="n">
-        <v>946</v>
+        <v>951</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5599,10 +5599,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5613,7 +5613,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
         <v>100</v>
@@ -5633,7 +5633,7 @@
         <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -5686,10 +5686,10 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6719</v>
+        <v>5088</v>
       </c>
       <c r="C2" t="n">
-        <v>10798</v>
+        <v>5853</v>
       </c>
       <c r="D2" t="n">
-        <v>27570</v>
+        <v>17472</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3640</v>
+        <v>3011</v>
       </c>
       <c r="C3" t="n">
-        <v>5983</v>
+        <v>4838</v>
       </c>
       <c r="D3" t="n">
-        <v>8522</v>
+        <v>9103</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1937</v>
+        <v>1686</v>
       </c>
       <c r="C4" t="n">
-        <v>4330</v>
+        <v>4465</v>
       </c>
       <c r="D4" t="n">
-        <v>2634</v>
+        <v>3437</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>910</v>
+        <v>750</v>
       </c>
       <c r="C5" t="n">
-        <v>2191</v>
+        <v>3136</v>
       </c>
       <c r="D5" t="n">
-        <v>1135</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>297</v>
+        <v>261</v>
       </c>
       <c r="C6" t="n">
-        <v>874</v>
+        <v>1626</v>
       </c>
       <c r="D6" t="n">
-        <v>760</v>
+        <v>773</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C7" t="n">
-        <v>295</v>
+        <v>506</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6000,7 +6000,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6684</v>
+        <v>5382</v>
       </c>
       <c r="C2" t="n">
-        <v>6129</v>
+        <v>7595</v>
       </c>
       <c r="D2" t="n">
-        <v>30289</v>
+        <v>17584</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4306</v>
+        <v>3347</v>
       </c>
       <c r="C3" t="n">
-        <v>7596</v>
+        <v>4668</v>
       </c>
       <c r="D3" t="n">
-        <v>11233</v>
+        <v>9839</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2452</v>
+        <v>2037</v>
       </c>
       <c r="C4" t="n">
-        <v>5255</v>
+        <v>4597</v>
       </c>
       <c r="D4" t="n">
-        <v>3797</v>
+        <v>4441</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1262</v>
+        <v>1086</v>
       </c>
       <c r="C5" t="n">
-        <v>3418</v>
+        <v>3849</v>
       </c>
       <c r="D5" t="n">
-        <v>1402</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>563</v>
+        <v>467</v>
       </c>
       <c r="C6" t="n">
-        <v>1621</v>
+        <v>2461</v>
       </c>
       <c r="D6" t="n">
-        <v>813</v>
+        <v>857</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="C7" t="n">
-        <v>623</v>
+        <v>1131</v>
       </c>
       <c r="D7" t="n">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>262</v>
+        <v>374</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6238,7 +6238,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5767</v>
+        <v>4309</v>
       </c>
       <c r="C2" t="n">
-        <v>8209</v>
+        <v>4011</v>
       </c>
       <c r="D2" t="n">
-        <v>28603</v>
+        <v>17911</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4491</v>
+        <v>3592</v>
       </c>
       <c r="C3" t="n">
-        <v>5882</v>
+        <v>5406</v>
       </c>
       <c r="D3" t="n">
-        <v>13473</v>
+        <v>10369</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2884</v>
+        <v>2288</v>
       </c>
       <c r="C4" t="n">
-        <v>6471</v>
+        <v>4540</v>
       </c>
       <c r="D4" t="n">
-        <v>5109</v>
+        <v>5342</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1632</v>
+        <v>1367</v>
       </c>
       <c r="C5" t="n">
-        <v>4352</v>
+        <v>4134</v>
       </c>
       <c r="D5" t="n">
-        <v>1782</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>822</v>
+        <v>693</v>
       </c>
       <c r="C6" t="n">
-        <v>2535</v>
+        <v>3165</v>
       </c>
       <c r="D6" t="n">
-        <v>909</v>
+        <v>992</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>326</v>
+        <v>272</v>
       </c>
       <c r="C7" t="n">
-        <v>1150</v>
+        <v>1821</v>
       </c>
       <c r="D7" t="n">
-        <v>590</v>
+        <v>601</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>445</v>
+        <v>748</v>
       </c>
       <c r="D8" t="n">
-        <v>413</v>
+        <v>403</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>235</v>
+        <v>289</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -6507,7 +6507,7 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
         <v>202</v>
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6577,7 +6577,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -6591,7 +6591,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
@@ -6650,7 +6650,7 @@
         <v>91</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_50_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_50_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4518</v>
+        <v>873</v>
       </c>
       <c r="C2" t="n">
-        <v>8477</v>
+        <v>2095</v>
       </c>
       <c r="D2" t="n">
-        <v>27571</v>
+        <v>16175</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3234</v>
+        <v>1859</v>
       </c>
       <c r="C3" t="n">
-        <v>4120</v>
+        <v>4111</v>
       </c>
       <c r="D3" t="n">
-        <v>10741</v>
+        <v>15618</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2488</v>
+        <v>1403</v>
       </c>
       <c r="C4" t="n">
-        <v>4894</v>
+        <v>5575</v>
       </c>
       <c r="D4" t="n">
-        <v>5996</v>
+        <v>7138</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1570</v>
+        <v>610</v>
       </c>
       <c r="C5" t="n">
-        <v>4211</v>
+        <v>3149</v>
       </c>
       <c r="D5" t="n">
-        <v>2601</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>908</v>
+        <v>257</v>
       </c>
       <c r="C6" t="n">
-        <v>3605</v>
+        <v>1227</v>
       </c>
       <c r="D6" t="n">
-        <v>1150</v>
+        <v>770</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>415</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>2465</v>
+        <v>496</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>499</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>152</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>1234</v>
+        <v>330</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>370</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>495</v>
+        <v>293</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>214</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>37</v>
-      </c>
-      <c r="D17" t="n">
-        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4910</v>
+        <v>1772</v>
       </c>
       <c r="C2" t="n">
-        <v>5565</v>
+        <v>3635</v>
       </c>
       <c r="D2" t="n">
-        <v>26188</v>
+        <v>23000</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3107</v>
+        <v>1165</v>
       </c>
       <c r="C3" t="n">
-        <v>5340</v>
+        <v>2623</v>
       </c>
       <c r="D3" t="n">
-        <v>12308</v>
+        <v>14582</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2401</v>
+        <v>1417</v>
       </c>
       <c r="C4" t="n">
-        <v>4381</v>
+        <v>4629</v>
       </c>
       <c r="D4" t="n">
-        <v>6588</v>
+        <v>8549</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1732</v>
+        <v>864</v>
       </c>
       <c r="C5" t="n">
-        <v>4438</v>
+        <v>4441</v>
       </c>
       <c r="D5" t="n">
-        <v>3018</v>
+        <v>2994</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1094</v>
+        <v>383</v>
       </c>
       <c r="C6" t="n">
-        <v>3802</v>
+        <v>2221</v>
       </c>
       <c r="D6" t="n">
-        <v>1357</v>
+        <v>997</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>555</v>
+        <v>152</v>
       </c>
       <c r="C7" t="n">
-        <v>2966</v>
+        <v>866</v>
       </c>
       <c r="D7" t="n">
-        <v>718</v>
+        <v>543</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>229</v>
+        <v>79</v>
       </c>
       <c r="C8" t="n">
-        <v>1740</v>
+        <v>414</v>
       </c>
       <c r="D8" t="n">
-        <v>458</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="C9" t="n">
-        <v>794</v>
+        <v>311</v>
       </c>
       <c r="D9" t="n">
-        <v>316</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>335</v>
+        <v>250</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>219</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>179</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6277</v>
+        <v>911</v>
       </c>
       <c r="C2" t="n">
-        <v>7044</v>
+        <v>1459</v>
       </c>
       <c r="D2" t="n">
-        <v>35744</v>
+        <v>15478</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3133</v>
+        <v>1294</v>
       </c>
       <c r="C3" t="n">
-        <v>4822</v>
+        <v>2918</v>
       </c>
       <c r="D3" t="n">
-        <v>13185</v>
+        <v>15262</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2294</v>
+        <v>1519</v>
       </c>
       <c r="C4" t="n">
-        <v>4662</v>
+        <v>4149</v>
       </c>
       <c r="D4" t="n">
-        <v>7148</v>
+        <v>9394</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1797</v>
+        <v>867</v>
       </c>
       <c r="C5" t="n">
-        <v>4279</v>
+        <v>5044</v>
       </c>
       <c r="D5" t="n">
-        <v>3440</v>
+        <v>3444</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1227</v>
+        <v>318</v>
       </c>
       <c r="C6" t="n">
-        <v>4030</v>
+        <v>2985</v>
       </c>
       <c r="D6" t="n">
-        <v>1549</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>687</v>
+        <v>75</v>
       </c>
       <c r="C7" t="n">
-        <v>3271</v>
+        <v>888</v>
       </c>
       <c r="D7" t="n">
-        <v>791</v>
+        <v>569</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>313</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>2219</v>
+        <v>458</v>
       </c>
       <c r="D8" t="n">
-        <v>489</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>123</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>1138</v>
+        <v>245</v>
       </c>
       <c r="D9" t="n">
-        <v>327</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>498</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>254</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>239</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>154</v>
+        <v>88</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>69</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5722</v>
+        <v>785</v>
       </c>
       <c r="C2" t="n">
-        <v>4789</v>
+        <v>7398</v>
       </c>
       <c r="D2" t="n">
-        <v>29228</v>
+        <v>22106</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3929</v>
+        <v>945</v>
       </c>
       <c r="C3" t="n">
-        <v>7398</v>
+        <v>1865</v>
       </c>
       <c r="D3" t="n">
-        <v>14220</v>
+        <v>14344</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1660</v>
+        <v>1257</v>
       </c>
       <c r="C4" t="n">
-        <v>6658</v>
+        <v>3417</v>
       </c>
       <c r="D4" t="n">
-        <v>7043</v>
+        <v>10178</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1133</v>
+        <v>1040</v>
       </c>
       <c r="C5" t="n">
-        <v>3949</v>
+        <v>4563</v>
       </c>
       <c r="D5" t="n">
-        <v>2442</v>
+        <v>4367</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>634</v>
+        <v>501</v>
       </c>
       <c r="C6" t="n">
-        <v>3205</v>
+        <v>3990</v>
       </c>
       <c r="D6" t="n">
-        <v>775</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>289</v>
+        <v>147</v>
       </c>
       <c r="C7" t="n">
-        <v>2174</v>
+        <v>1891</v>
       </c>
       <c r="D7" t="n">
-        <v>479</v>
+        <v>628</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>113</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>1115</v>
+        <v>656</v>
       </c>
       <c r="D8" t="n">
-        <v>320</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>488</v>
+        <v>333</v>
       </c>
       <c r="D9" t="n">
-        <v>248</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>199</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>103</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3526</v>
+        <v>422</v>
       </c>
       <c r="C2" t="n">
-        <v>2228</v>
+        <v>3258</v>
       </c>
       <c r="D2" t="n">
-        <v>20314</v>
+        <v>16206</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4040</v>
+        <v>769</v>
       </c>
       <c r="C3" t="n">
-        <v>5646</v>
+        <v>4073</v>
       </c>
       <c r="D3" t="n">
-        <v>15442</v>
+        <v>14612</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2198</v>
+        <v>1055</v>
       </c>
       <c r="C4" t="n">
-        <v>7052</v>
+        <v>2684</v>
       </c>
       <c r="D4" t="n">
-        <v>8066</v>
+        <v>10743</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1264</v>
+        <v>1090</v>
       </c>
       <c r="C5" t="n">
-        <v>5174</v>
+        <v>4137</v>
       </c>
       <c r="D5" t="n">
-        <v>2988</v>
+        <v>5057</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>751</v>
+        <v>625</v>
       </c>
       <c r="C6" t="n">
-        <v>3657</v>
+        <v>4372</v>
       </c>
       <c r="D6" t="n">
-        <v>948</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>273</v>
+        <v>176</v>
       </c>
       <c r="C7" t="n">
-        <v>2616</v>
+        <v>2717</v>
       </c>
       <c r="D7" t="n">
-        <v>522</v>
+        <v>701</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>96</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>1460</v>
+        <v>991</v>
       </c>
       <c r="D8" t="n">
-        <v>334</v>
+        <v>498</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>536</v>
+        <v>437</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>381</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3477</v>
+        <v>986</v>
       </c>
       <c r="C2" t="n">
-        <v>8751</v>
+        <v>4515</v>
       </c>
       <c r="D2" t="n">
-        <v>21022</v>
+        <v>17389</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3209</v>
+        <v>518</v>
       </c>
       <c r="C3" t="n">
-        <v>3528</v>
+        <v>3245</v>
       </c>
       <c r="D3" t="n">
-        <v>15229</v>
+        <v>13836</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2588</v>
+        <v>818</v>
       </c>
       <c r="C4" t="n">
-        <v>6271</v>
+        <v>3334</v>
       </c>
       <c r="D4" t="n">
-        <v>9024</v>
+        <v>11084</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1477</v>
+        <v>992</v>
       </c>
       <c r="C5" t="n">
-        <v>5949</v>
+        <v>3339</v>
       </c>
       <c r="D5" t="n">
-        <v>3648</v>
+        <v>5831</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>885</v>
+        <v>758</v>
       </c>
       <c r="C6" t="n">
-        <v>4341</v>
+        <v>4259</v>
       </c>
       <c r="D6" t="n">
-        <v>1257</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>408</v>
+        <v>312</v>
       </c>
       <c r="C7" t="n">
-        <v>3063</v>
+        <v>3488</v>
       </c>
       <c r="D7" t="n">
-        <v>575</v>
+        <v>851</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>139</v>
+        <v>87</v>
       </c>
       <c r="C8" t="n">
-        <v>1949</v>
+        <v>1717</v>
       </c>
       <c r="D8" t="n">
-        <v>354</v>
+        <v>520</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="C9" t="n">
-        <v>899</v>
+        <v>667</v>
       </c>
       <c r="D9" t="n">
-        <v>262</v>
+        <v>392</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>347</v>
+        <v>310</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>191</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2063</v>
+        <v>638</v>
       </c>
       <c r="C2" t="n">
-        <v>4016</v>
+        <v>2239</v>
       </c>
       <c r="D2" t="n">
-        <v>14489</v>
+        <v>12380</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3157</v>
+        <v>800</v>
       </c>
       <c r="C3" t="n">
-        <v>5211</v>
+        <v>3864</v>
       </c>
       <c r="D3" t="n">
-        <v>15512</v>
+        <v>15105</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2860</v>
+        <v>1312</v>
       </c>
       <c r="C4" t="n">
-        <v>5881</v>
+        <v>4592</v>
       </c>
       <c r="D4" t="n">
-        <v>9900</v>
+        <v>11579</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1549</v>
+        <v>792</v>
       </c>
       <c r="C5" t="n">
-        <v>6905</v>
+        <v>5441</v>
       </c>
       <c r="D5" t="n">
-        <v>3862</v>
+        <v>5403</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>736</v>
+        <v>288</v>
       </c>
       <c r="C6" t="n">
-        <v>5344</v>
+        <v>4586</v>
       </c>
       <c r="D6" t="n">
-        <v>1237</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>128</v>
+        <v>80</v>
       </c>
       <c r="C7" t="n">
-        <v>3339</v>
+        <v>1682</v>
       </c>
       <c r="D7" t="n">
-        <v>575</v>
+        <v>643</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="C8" t="n">
-        <v>1492</v>
+        <v>653</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>340</v>
+        <v>303</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2186</v>
+        <v>349</v>
       </c>
       <c r="C2" t="n">
-        <v>5223</v>
+        <v>1636</v>
       </c>
       <c r="D2" t="n">
-        <v>12853</v>
+        <v>9661</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2307</v>
+        <v>613</v>
       </c>
       <c r="C3" t="n">
-        <v>4139</v>
+        <v>2682</v>
       </c>
       <c r="D3" t="n">
-        <v>14330</v>
+        <v>13586</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2635</v>
+        <v>890</v>
       </c>
       <c r="C4" t="n">
-        <v>5493</v>
+        <v>3956</v>
       </c>
       <c r="D4" t="n">
-        <v>10514</v>
+        <v>11381</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1850</v>
+        <v>735</v>
       </c>
       <c r="C5" t="n">
-        <v>6299</v>
+        <v>4459</v>
       </c>
       <c r="D5" t="n">
-        <v>4709</v>
+        <v>5727</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>947</v>
+        <v>292</v>
       </c>
       <c r="C6" t="n">
-        <v>6072</v>
+        <v>4147</v>
       </c>
       <c r="D6" t="n">
-        <v>1573</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>282</v>
+        <v>72</v>
       </c>
       <c r="C7" t="n">
-        <v>4175</v>
+        <v>2164</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>644</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>2223</v>
+        <v>714</v>
       </c>
       <c r="D8" t="n">
-        <v>391</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>719</v>
+        <v>280</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>240</v>
+        <v>139</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>136</v>
+        <v>80</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1544</v>
+        <v>582</v>
       </c>
       <c r="C2" t="n">
-        <v>3937</v>
+        <v>4118</v>
       </c>
       <c r="D2" t="n">
-        <v>9180</v>
+        <v>14425</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1985</v>
+        <v>403</v>
       </c>
       <c r="C3" t="n">
-        <v>4186</v>
+        <v>1802</v>
       </c>
       <c r="D3" t="n">
-        <v>13373</v>
+        <v>12057</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2337</v>
+        <v>663</v>
       </c>
       <c r="C4" t="n">
-        <v>4978</v>
+        <v>3165</v>
       </c>
       <c r="D4" t="n">
-        <v>10808</v>
+        <v>11349</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1986</v>
+        <v>736</v>
       </c>
       <c r="C5" t="n">
-        <v>6055</v>
+        <v>4086</v>
       </c>
       <c r="D5" t="n">
-        <v>5324</v>
+        <v>6638</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1123</v>
+        <v>458</v>
       </c>
       <c r="C6" t="n">
-        <v>6398</v>
+        <v>4307</v>
       </c>
       <c r="D6" t="n">
-        <v>1855</v>
+        <v>2667</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>265</v>
+        <v>151</v>
       </c>
       <c r="C7" t="n">
-        <v>4943</v>
+        <v>3214</v>
       </c>
       <c r="D7" t="n">
-        <v>733</v>
+        <v>886</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="C8" t="n">
-        <v>2771</v>
+        <v>1431</v>
       </c>
       <c r="D8" t="n">
-        <v>414</v>
+        <v>379</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>856</v>
+        <v>482</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>243</v>
+        <v>202</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>103</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2746</v>
+        <v>851</v>
       </c>
       <c r="C2" t="n">
-        <v>6769</v>
+        <v>5519</v>
       </c>
       <c r="D2" t="n">
-        <v>10607</v>
+        <v>21474</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1534</v>
+        <v>400</v>
       </c>
       <c r="C3" t="n">
-        <v>3659</v>
+        <v>2606</v>
       </c>
       <c r="D3" t="n">
-        <v>12013</v>
+        <v>11568</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1939</v>
+        <v>472</v>
       </c>
       <c r="C4" t="n">
-        <v>4532</v>
+        <v>2366</v>
       </c>
       <c r="D4" t="n">
-        <v>10848</v>
+        <v>11133</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1924</v>
+        <v>641</v>
       </c>
       <c r="C5" t="n">
-        <v>5484</v>
+        <v>3523</v>
       </c>
       <c r="D5" t="n">
-        <v>5848</v>
+        <v>7186</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1323</v>
+        <v>542</v>
       </c>
       <c r="C6" t="n">
-        <v>6207</v>
+        <v>4150</v>
       </c>
       <c r="D6" t="n">
-        <v>2297</v>
+        <v>3316</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>482</v>
+        <v>258</v>
       </c>
       <c r="C7" t="n">
-        <v>5497</v>
+        <v>3748</v>
       </c>
       <c r="D7" t="n">
-        <v>868</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>3584</v>
+        <v>2269</v>
       </c>
       <c r="D8" t="n">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>1502</v>
+        <v>909</v>
       </c>
       <c r="D9" t="n">
-        <v>303</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>431</v>
+        <v>322</v>
       </c>
       <c r="D10" t="n">
-        <v>188</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4418</v>
+        <v>3131</v>
       </c>
       <c r="C2" t="n">
-        <v>13308</v>
+        <v>3754</v>
       </c>
       <c r="D2" t="n">
-        <v>10561</v>
+        <v>8265</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1942</v>
+        <v>608</v>
       </c>
       <c r="C2" t="n">
-        <v>3791</v>
+        <v>17478</v>
       </c>
       <c r="D2" t="n">
-        <v>7806</v>
+        <v>25174</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2181</v>
+        <v>487</v>
       </c>
       <c r="C3" t="n">
-        <v>4715</v>
+        <v>3496</v>
       </c>
       <c r="D3" t="n">
-        <v>12940</v>
+        <v>12309</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2747</v>
+        <v>383</v>
       </c>
       <c r="C4" t="n">
-        <v>6404</v>
+        <v>2436</v>
       </c>
       <c r="D4" t="n">
-        <v>11032</v>
+        <v>10758</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1293</v>
+        <v>520</v>
       </c>
       <c r="C5" t="n">
-        <v>8438</v>
+        <v>2894</v>
       </c>
       <c r="D5" t="n">
-        <v>5392</v>
+        <v>7611</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>445</v>
+        <v>547</v>
       </c>
       <c r="C6" t="n">
-        <v>6664</v>
+        <v>3819</v>
       </c>
       <c r="D6" t="n">
-        <v>1865</v>
+        <v>3833</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>93</v>
+        <v>340</v>
       </c>
       <c r="C7" t="n">
-        <v>3512</v>
+        <v>3890</v>
       </c>
       <c r="D7" t="n">
-        <v>548</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>132</v>
       </c>
       <c r="C8" t="n">
-        <v>1471</v>
+        <v>2920</v>
       </c>
       <c r="D8" t="n">
-        <v>296</v>
+        <v>551</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="C9" t="n">
-        <v>422</v>
+        <v>1481</v>
       </c>
       <c r="D9" t="n">
-        <v>184</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>160</v>
+        <v>557</v>
       </c>
       <c r="D10" t="n">
-        <v>133</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>91</v>
+        <v>209</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6097</v>
+        <v>4505</v>
       </c>
       <c r="C2" t="n">
-        <v>6759</v>
+        <v>7195</v>
       </c>
       <c r="D2" t="n">
-        <v>14351</v>
+        <v>29362</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1878</v>
+        <v>1036</v>
       </c>
       <c r="C3" t="n">
-        <v>6707</v>
+        <v>1482</v>
       </c>
       <c r="D3" t="n">
-        <v>2413</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>275</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>209</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4335</v>
+        <v>2316</v>
       </c>
       <c r="C2" t="n">
-        <v>6890</v>
+        <v>3775</v>
       </c>
       <c r="D2" t="n">
-        <v>25082</v>
+        <v>21684</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3271</v>
+        <v>2352</v>
       </c>
       <c r="C3" t="n">
-        <v>5809</v>
+        <v>4239</v>
       </c>
       <c r="D3" t="n">
-        <v>4240</v>
+        <v>6476</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>850</v>
+        <v>506</v>
       </c>
       <c r="C4" t="n">
-        <v>3973</v>
+        <v>972</v>
       </c>
       <c r="D4" t="n">
-        <v>1667</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>135</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>247</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>190</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5518</v>
+        <v>3091</v>
       </c>
       <c r="C2" t="n">
-        <v>7704</v>
+        <v>2983</v>
       </c>
       <c r="D2" t="n">
-        <v>20124</v>
+        <v>26739</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3148</v>
+        <v>1925</v>
       </c>
       <c r="C3" t="n">
-        <v>5539</v>
+        <v>3408</v>
       </c>
       <c r="D3" t="n">
-        <v>7269</v>
+        <v>8554</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1721</v>
+        <v>1253</v>
       </c>
       <c r="C4" t="n">
-        <v>4874</v>
+        <v>2927</v>
       </c>
       <c r="D4" t="n">
-        <v>2110</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>403</v>
+        <v>266</v>
       </c>
       <c r="C5" t="n">
-        <v>2271</v>
+        <v>650</v>
       </c>
       <c r="D5" t="n">
-        <v>1235</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>259</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>799</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>353</v>
+        <v>288</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>219</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4874</v>
+        <v>2656</v>
       </c>
       <c r="C2" t="n">
-        <v>6021</v>
+        <v>5354</v>
       </c>
       <c r="D2" t="n">
-        <v>19094</v>
+        <v>22442</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3478</v>
+        <v>2056</v>
       </c>
       <c r="C3" t="n">
-        <v>5782</v>
+        <v>2740</v>
       </c>
       <c r="D3" t="n">
-        <v>8711</v>
+        <v>10847</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2040</v>
+        <v>1375</v>
       </c>
       <c r="C4" t="n">
-        <v>5076</v>
+        <v>3143</v>
       </c>
       <c r="D4" t="n">
-        <v>2986</v>
+        <v>3497</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>872</v>
+        <v>642</v>
       </c>
       <c r="C5" t="n">
-        <v>3573</v>
+        <v>1904</v>
       </c>
       <c r="D5" t="n">
-        <v>1336</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>238</v>
+        <v>171</v>
       </c>
       <c r="C6" t="n">
-        <v>1283</v>
+        <v>466</v>
       </c>
       <c r="D6" t="n">
-        <v>951</v>
+        <v>841</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>293</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>377</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="C9" t="n">
-        <v>307</v>
+        <v>253</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>195</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5088</v>
+        <v>2401</v>
       </c>
       <c r="C2" t="n">
-        <v>5853</v>
+        <v>6816</v>
       </c>
       <c r="D2" t="n">
-        <v>17472</v>
+        <v>33318</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3011</v>
+        <v>1930</v>
       </c>
       <c r="C3" t="n">
-        <v>4838</v>
+        <v>3589</v>
       </c>
       <c r="D3" t="n">
-        <v>9103</v>
+        <v>12025</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1686</v>
+        <v>1473</v>
       </c>
       <c r="C4" t="n">
-        <v>4465</v>
+        <v>2853</v>
       </c>
       <c r="D4" t="n">
-        <v>3437</v>
+        <v>4697</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>750</v>
+        <v>865</v>
       </c>
       <c r="C5" t="n">
-        <v>3136</v>
+        <v>2530</v>
       </c>
       <c r="D5" t="n">
-        <v>1269</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>261</v>
+        <v>357</v>
       </c>
       <c r="C6" t="n">
-        <v>1626</v>
+        <v>1206</v>
       </c>
       <c r="D6" t="n">
-        <v>773</v>
+        <v>902</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="C7" t="n">
-        <v>506</v>
+        <v>381</v>
       </c>
       <c r="D7" t="n">
-        <v>517</v>
+        <v>621</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>300</v>
       </c>
       <c r="D8" t="n">
-        <v>357</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>278</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>345</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5382</v>
+        <v>1694</v>
       </c>
       <c r="C2" t="n">
-        <v>7595</v>
+        <v>4942</v>
       </c>
       <c r="D2" t="n">
-        <v>17584</v>
+        <v>27074</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3347</v>
+        <v>1768</v>
       </c>
       <c r="C3" t="n">
-        <v>4668</v>
+        <v>4529</v>
       </c>
       <c r="D3" t="n">
-        <v>9839</v>
+        <v>14263</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2037</v>
+        <v>1442</v>
       </c>
       <c r="C4" t="n">
-        <v>4597</v>
+        <v>3147</v>
       </c>
       <c r="D4" t="n">
-        <v>4441</v>
+        <v>5775</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1086</v>
+        <v>1015</v>
       </c>
       <c r="C5" t="n">
-        <v>3849</v>
+        <v>2641</v>
       </c>
       <c r="D5" t="n">
-        <v>1667</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>467</v>
+        <v>530</v>
       </c>
       <c r="C6" t="n">
-        <v>2461</v>
+        <v>1841</v>
       </c>
       <c r="D6" t="n">
-        <v>857</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>155</v>
+        <v>206</v>
       </c>
       <c r="C7" t="n">
-        <v>1131</v>
+        <v>777</v>
       </c>
       <c r="D7" t="n">
-        <v>554</v>
+        <v>661</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="C8" t="n">
-        <v>374</v>
+        <v>334</v>
       </c>
       <c r="D8" t="n">
-        <v>383</v>
+        <v>470</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>287</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>353</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>171</v>
+        <v>244</v>
       </c>
       <c r="D10" t="n">
-        <v>234</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>193</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>263</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>154</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>209</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4309</v>
+        <v>1611</v>
       </c>
       <c r="C2" t="n">
-        <v>4011</v>
+        <v>2965</v>
       </c>
       <c r="D2" t="n">
-        <v>17911</v>
+        <v>21146</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3592</v>
+        <v>2478</v>
       </c>
       <c r="C3" t="n">
-        <v>5406</v>
+        <v>6333</v>
       </c>
       <c r="D3" t="n">
-        <v>10369</v>
+        <v>15757</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2288</v>
+        <v>937</v>
       </c>
       <c r="C4" t="n">
-        <v>4540</v>
+        <v>4559</v>
       </c>
       <c r="D4" t="n">
-        <v>5342</v>
+        <v>5411</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1367</v>
+        <v>489</v>
       </c>
       <c r="C5" t="n">
-        <v>4134</v>
+        <v>1804</v>
       </c>
       <c r="D5" t="n">
-        <v>2106</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>693</v>
+        <v>190</v>
       </c>
       <c r="C6" t="n">
-        <v>3165</v>
+        <v>761</v>
       </c>
       <c r="D6" t="n">
-        <v>992</v>
+        <v>647</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>272</v>
+        <v>90</v>
       </c>
       <c r="C7" t="n">
-        <v>1821</v>
+        <v>327</v>
       </c>
       <c r="D7" t="n">
-        <v>601</v>
+        <v>460</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>748</v>
+        <v>281</v>
       </c>
       <c r="D8" t="n">
-        <v>403</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>289</v>
+        <v>239</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
